--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132985582</v>
+        <v>132966472</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,45 +1607,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633593</v>
+        <v>633653</v>
       </c>
       <c r="R10" t="n">
-        <v>7009766</v>
+        <v>7009392</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,12 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre spår på halvstubbe, björk.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1691,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132966472</v>
+        <v>132985582</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,37 +1714,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633653</v>
+        <v>633593</v>
       </c>
       <c r="R11" t="n">
-        <v>7009392</v>
+        <v>7009766</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1791,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre spår på halvstubbe, björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,12 +1811,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2152,57 +2152,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132972224</v>
+        <v>132985568</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633696</v>
+        <v>633641</v>
       </c>
       <c r="R15" t="n">
-        <v>7009597</v>
+        <v>7009436</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,60 +2247,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132985568</v>
+        <v>132972224</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633641</v>
+        <v>633696</v>
       </c>
       <c r="R16" t="n">
-        <v>7009436</v>
+        <v>7009597</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,12 +2363,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2589,57 +2589,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132975429</v>
+        <v>132985585</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633629</v>
+        <v>633586</v>
       </c>
       <c r="R19" t="n">
-        <v>7009730</v>
+        <v>7009542</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2668,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,12 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>500+</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,19 +2684,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132985585</v>
+        <v>132985572</v>
       </c>
       <c r="B20" t="n">
         <v>79333</v>
@@ -2745,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633586</v>
+        <v>633848</v>
       </c>
       <c r="R20" t="n">
-        <v>7009542</v>
+        <v>7009460</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2780,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,48 +2803,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132985572</v>
+        <v>132975429</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633848</v>
+        <v>633629</v>
       </c>
       <c r="R21" t="n">
-        <v>7009460</v>
+        <v>7009730</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2892,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>500+</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,69 +2912,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132972743</v>
+        <v>132977419</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633688</v>
+        <v>633529</v>
       </c>
       <c r="R22" t="n">
-        <v>7009606</v>
+        <v>7009795</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3003,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,14 +3024,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132973056</v>
+        <v>132972743</v>
       </c>
       <c r="B23" t="n">
         <v>99130</v>
@@ -3070,7 +3061,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3084,10 +3075,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633682</v>
+        <v>633688</v>
       </c>
       <c r="R23" t="n">
-        <v>7009654</v>
+        <v>7009606</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3119,7 +3110,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3120,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,48 +3147,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132977419</v>
+        <v>132973056</v>
       </c>
       <c r="B24" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633529</v>
+        <v>633682</v>
       </c>
       <c r="R24" t="n">
-        <v>7009795</v>
+        <v>7009654</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3806,56 +3806,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132985575</v>
+        <v>132977000</v>
       </c>
       <c r="B30" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>633690</v>
+        <v>633575</v>
       </c>
       <c r="R30" t="n">
-        <v>7009620</v>
+        <v>7009754</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,7 +3885,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3895,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3909,69 +3910,68 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132977000</v>
+        <v>132985575</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633575</v>
+        <v>633690</v>
       </c>
       <c r="R31" t="n">
-        <v>7009754</v>
+        <v>7009620</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4025,12 +4025,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4380,32 +4380,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132985579</v>
+        <v>132985583</v>
       </c>
       <c r="B35" t="n">
-        <v>92217</v>
+        <v>97995</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633738</v>
+        <v>633562</v>
       </c>
       <c r="R35" t="n">
-        <v>7009697</v>
+        <v>7009789</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,32 +4487,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132985583</v>
+        <v>132985579</v>
       </c>
       <c r="B36" t="n">
-        <v>97995</v>
+        <v>92217</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633562</v>
+        <v>633738</v>
       </c>
       <c r="R36" t="n">
-        <v>7009789</v>
+        <v>7009697</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132985580</v>
+        <v>132985567</v>
       </c>
       <c r="B37" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4605,45 +4605,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633608</v>
+        <v>633458</v>
       </c>
       <c r="R37" t="n">
-        <v>7009719</v>
+        <v>7009474</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4672,7 +4664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4682,7 +4674,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4709,10 +4701,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132985567</v>
+        <v>132985580</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4720,37 +4712,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633458</v>
+        <v>633608</v>
       </c>
       <c r="R38" t="n">
-        <v>7009474</v>
+        <v>7009719</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4936,60 +4936,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132989700</v>
+        <v>132989693</v>
       </c>
       <c r="B40" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633634</v>
+        <v>633411</v>
       </c>
       <c r="R40" t="n">
-        <v>7009438</v>
+        <v>7009457</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +5006,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5016,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5037,7 +5025,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5049,55 +5036,67 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132989693</v>
+        <v>132989700</v>
       </c>
       <c r="B41" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>633411</v>
+        <v>633634</v>
       </c>
       <c r="R41" t="n">
-        <v>7009457</v>
+        <v>7009438</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5126,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5136,7 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5145,6 +5144,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6444,46 +6444,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132989719</v>
+        <v>132989695</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6491,13 +6487,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>633562</v>
+        <v>633396</v>
       </c>
       <c r="R53" t="n">
-        <v>7009774</v>
+        <v>7009466</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6526,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6532,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6545,7 +6546,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6557,17 +6557,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132989704</v>
+        <v>132989715</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6575,37 +6575,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633780</v>
+        <v>633701</v>
       </c>
       <c r="R54" t="n">
-        <v>7009330</v>
+        <v>7009718</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6634,7 +6642,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6644,7 +6652,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6671,10 +6684,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132989695</v>
+        <v>132989704</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,42 +6695,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633396</v>
+        <v>633780</v>
       </c>
       <c r="R55" t="n">
-        <v>7009466</v>
+        <v>7009330</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6749,7 +6754,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6759,12 +6764,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6791,42 +6791,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132989715</v>
+        <v>132989719</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6834,10 +6838,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>633701</v>
+        <v>633562</v>
       </c>
       <c r="R56" t="n">
-        <v>7009718</v>
+        <v>7009774</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6869,7 +6873,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6879,12 +6883,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6893,6 +6892,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6904,39 +6904,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132989690</v>
+        <v>132989694</v>
       </c>
       <c r="B57" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633278</v>
+        <v>633407</v>
       </c>
       <c r="R57" t="n">
-        <v>7009482</v>
+        <v>7009456</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7018,32 +7018,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132989694</v>
+        <v>132989690</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7053,13 +7053,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>633407</v>
+        <v>633278</v>
       </c>
       <c r="R58" t="n">
-        <v>7009456</v>
+        <v>7009482</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8122,10 +8122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133067792</v>
+        <v>133067806</v>
       </c>
       <c r="B68" t="n">
-        <v>89300</v>
+        <v>92217</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8157,13 +8157,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>633688</v>
+        <v>633605</v>
       </c>
       <c r="R68" t="n">
-        <v>7009675</v>
+        <v>7009728</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133067818</v>
+        <v>133067792</v>
       </c>
       <c r="B69" t="n">
         <v>89300</v>
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>633537</v>
+        <v>633688</v>
       </c>
       <c r="R69" t="n">
-        <v>7009784</v>
+        <v>7009675</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133067754</v>
+        <v>133067818</v>
       </c>
       <c r="B70" t="n">
-        <v>92217</v>
+        <v>89300</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8351,13 +8351,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>633335</v>
+        <v>633537</v>
       </c>
       <c r="R70" t="n">
-        <v>7009491</v>
+        <v>7009784</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133067806</v>
+        <v>133067754</v>
       </c>
       <c r="B71" t="n">
         <v>92217</v>
@@ -8448,13 +8448,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>633605</v>
+        <v>633335</v>
       </c>
       <c r="R71" t="n">
-        <v>7009728</v>
+        <v>7009491</v>
       </c>
       <c r="S71" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9600,32 +9600,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133067797</v>
+        <v>133067803</v>
       </c>
       <c r="B83" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9635,13 +9635,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>633707</v>
+        <v>633650</v>
       </c>
       <c r="R83" t="n">
-        <v>7009722</v>
+        <v>7009698</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9671,11 +9671,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9702,32 +9697,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133067803</v>
+        <v>133067797</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9737,13 +9732,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>633650</v>
+        <v>633707</v>
       </c>
       <c r="R84" t="n">
-        <v>7009698</v>
+        <v>7009722</v>
       </c>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9773,6 +9768,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9896,32 +9896,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133067766</v>
+        <v>133067800</v>
       </c>
       <c r="B86" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9931,13 +9931,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>633699</v>
+        <v>633706</v>
       </c>
       <c r="R86" t="n">
-        <v>7009355</v>
+        <v>7009741</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9967,11 +9967,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9998,10 +9993,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133067800</v>
+        <v>133067768</v>
       </c>
       <c r="B87" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10009,21 +10004,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10033,13 +10028,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>633706</v>
+        <v>633718</v>
       </c>
       <c r="R87" t="n">
-        <v>7009741</v>
+        <v>7009343</v>
       </c>
       <c r="S87" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10095,32 +10090,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133067768</v>
+        <v>133067766</v>
       </c>
       <c r="B88" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10130,10 +10125,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>633718</v>
+        <v>633699</v>
       </c>
       <c r="R88" t="n">
-        <v>7009343</v>
+        <v>7009355</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10166,6 +10161,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10682,10 +10682,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133067823</v>
+        <v>133067771</v>
       </c>
       <c r="B94" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10693,21 +10693,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10717,13 +10717,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>633543</v>
+        <v>633826</v>
       </c>
       <c r="R94" t="n">
-        <v>7009795</v>
+        <v>7009369</v>
       </c>
       <c r="S94" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10779,10 +10779,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133067773</v>
+        <v>133067826</v>
       </c>
       <c r="B95" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10790,21 +10790,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10814,13 +10814,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>633849</v>
+        <v>633546</v>
       </c>
       <c r="R95" t="n">
-        <v>7009402</v>
+        <v>7009736</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10876,10 +10876,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133067771</v>
+        <v>133067823</v>
       </c>
       <c r="B96" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,21 +10887,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10911,13 +10911,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>633826</v>
+        <v>633543</v>
       </c>
       <c r="R96" t="n">
-        <v>7009369</v>
+        <v>7009795</v>
       </c>
       <c r="S96" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10973,10 +10973,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133067826</v>
+        <v>133067794</v>
       </c>
       <c r="B97" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10984,21 +10984,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>633546</v>
+        <v>633693</v>
       </c>
       <c r="R97" t="n">
-        <v>7009736</v>
+        <v>7009699</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133067794</v>
+        <v>133067773</v>
       </c>
       <c r="B98" t="n">
         <v>79333</v>
@@ -11105,13 +11105,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>633693</v>
+        <v>633849</v>
       </c>
       <c r="R98" t="n">
-        <v>7009699</v>
+        <v>7009402</v>
       </c>
       <c r="S98" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11768,32 +11768,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133067763</v>
+        <v>133067783</v>
       </c>
       <c r="B105" t="n">
-        <v>80467</v>
+        <v>92217</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11803,13 +11803,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>633697</v>
+        <v>633708</v>
       </c>
       <c r="R105" t="n">
-        <v>7009345</v>
+        <v>7009648</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133067783</v>
+        <v>133067763</v>
       </c>
       <c r="B106" t="n">
-        <v>92217</v>
+        <v>80467</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11900,13 +11900,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>633708</v>
+        <v>633697</v>
       </c>
       <c r="R106" t="n">
-        <v>7009648</v>
+        <v>7009345</v>
       </c>
       <c r="S106" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12059,32 +12059,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133067819</v>
+        <v>133067775</v>
       </c>
       <c r="B108" t="n">
-        <v>80467</v>
+        <v>83181</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12094,13 +12094,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>633552</v>
+        <v>633854</v>
       </c>
       <c r="R108" t="n">
-        <v>7009791</v>
+        <v>7009413</v>
       </c>
       <c r="S108" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12156,32 +12156,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133067775</v>
+        <v>133067819</v>
       </c>
       <c r="B109" t="n">
-        <v>83181</v>
+        <v>80467</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12191,13 +12191,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>633854</v>
+        <v>633552</v>
       </c>
       <c r="R109" t="n">
-        <v>7009413</v>
+        <v>7009791</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132969284</v>
+        <v>132985571</v>
       </c>
       <c r="B5" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,37 +1064,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633653</v>
+        <v>633844</v>
       </c>
       <c r="R5" t="n">
-        <v>7009392</v>
+        <v>7009381</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,22 +1148,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132985571</v>
+        <v>132969284</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633844</v>
+        <v>633653</v>
       </c>
       <c r="R6" t="n">
-        <v>7009381</v>
+        <v>7009392</v>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,12 +1255,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132969471</v>
+        <v>132985568</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633840</v>
+        <v>633641</v>
       </c>
       <c r="R14" t="n">
-        <v>7009473</v>
+        <v>7009436</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,22 +2140,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132985568</v>
+        <v>132969471</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,37 +2163,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633641</v>
+        <v>633840</v>
       </c>
       <c r="R15" t="n">
-        <v>7009436</v>
+        <v>7009473</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,12 +2247,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2589,48 +2589,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132985585</v>
+        <v>132975429</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633586</v>
+        <v>633629</v>
       </c>
       <c r="R19" t="n">
-        <v>7009542</v>
+        <v>7009730</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2678,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>500+</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,19 +2698,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132985572</v>
+        <v>132985585</v>
       </c>
       <c r="B20" t="n">
         <v>79333</v>
@@ -2731,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633848</v>
+        <v>633586</v>
       </c>
       <c r="R20" t="n">
-        <v>7009460</v>
+        <v>7009542</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2766,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,57 +2817,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132975429</v>
+        <v>132985572</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633629</v>
+        <v>633848</v>
       </c>
       <c r="R21" t="n">
-        <v>7009730</v>
+        <v>7009460</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2882,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,12 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>500+</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,12 +2912,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3806,57 +3806,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132977000</v>
+        <v>132985575</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>633575</v>
+        <v>633690</v>
       </c>
       <c r="R30" t="n">
-        <v>7009754</v>
+        <v>7009620</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3885,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3895,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,68 +3909,69 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132985575</v>
+        <v>132977000</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633690</v>
+        <v>633575</v>
       </c>
       <c r="R31" t="n">
-        <v>7009620</v>
+        <v>7009754</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4025,12 +4025,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4380,32 +4380,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132985583</v>
+        <v>132985567</v>
       </c>
       <c r="B35" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4415,13 +4415,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633562</v>
+        <v>633458</v>
       </c>
       <c r="R35" t="n">
-        <v>7009789</v>
+        <v>7009474</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132985567</v>
+        <v>132985580</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4605,37 +4605,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633458</v>
+        <v>633608</v>
       </c>
       <c r="R37" t="n">
-        <v>7009474</v>
+        <v>7009719</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4664,7 +4672,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4674,7 +4682,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4701,56 +4709,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132985580</v>
+        <v>132985583</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633608</v>
+        <v>633562</v>
       </c>
       <c r="R38" t="n">
-        <v>7009719</v>
+        <v>7009789</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132989702</v>
+        <v>132989718</v>
       </c>
       <c r="B48" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,34 +5903,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>633642</v>
+        <v>633738</v>
       </c>
       <c r="R48" t="n">
-        <v>7009370</v>
+        <v>7009686</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5962,7 +5970,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5972,7 +5980,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5999,10 +6012,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132989718</v>
+        <v>132989702</v>
       </c>
       <c r="B49" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,42 +6023,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>633738</v>
+        <v>633642</v>
       </c>
       <c r="R49" t="n">
-        <v>7009686</v>
+        <v>7009370</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6077,7 +6082,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6087,12 +6092,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6444,42 +6444,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132989695</v>
+        <v>132989719</v>
       </c>
       <c r="B53" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6487,13 +6491,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>633396</v>
+        <v>633562</v>
       </c>
       <c r="R53" t="n">
-        <v>7009466</v>
+        <v>7009774</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6522,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,12 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6546,6 +6545,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6557,14 +6557,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132989715</v>
+        <v>132989695</v>
       </c>
       <c r="B54" t="n">
         <v>57958</v>
@@ -6597,7 +6597,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>633701</v>
+        <v>633396</v>
       </c>
       <c r="R54" t="n">
-        <v>7009718</v>
+        <v>7009466</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6684,10 +6684,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132989704</v>
+        <v>132989715</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6695,37 +6695,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>633780</v>
+        <v>633701</v>
       </c>
       <c r="R55" t="n">
-        <v>7009330</v>
+        <v>7009718</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6754,7 +6762,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6764,7 +6772,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6791,60 +6804,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132989719</v>
+        <v>132989704</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>633562</v>
+        <v>633780</v>
       </c>
       <c r="R56" t="n">
-        <v>7009774</v>
+        <v>7009330</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6873,7 +6874,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6883,7 +6884,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6892,7 +6893,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6904,39 +6904,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132989694</v>
+        <v>132989690</v>
       </c>
       <c r="B57" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633407</v>
+        <v>633278</v>
       </c>
       <c r="R57" t="n">
-        <v>7009456</v>
+        <v>7009482</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7018,32 +7018,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132989690</v>
+        <v>132989694</v>
       </c>
       <c r="B58" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7053,13 +7053,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>633278</v>
+        <v>633407</v>
       </c>
       <c r="R58" t="n">
-        <v>7009482</v>
+        <v>7009456</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7579,53 +7579,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132989703</v>
+        <v>132989689</v>
       </c>
       <c r="B63" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>633657</v>
+        <v>633212</v>
       </c>
       <c r="R63" t="n">
-        <v>7009340</v>
+        <v>7009460</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7657,7 +7649,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7667,7 +7659,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7694,45 +7686,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132989689</v>
+        <v>132989703</v>
       </c>
       <c r="B64" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>633212</v>
+        <v>633657</v>
       </c>
       <c r="R64" t="n">
-        <v>7009460</v>
+        <v>7009340</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7801,32 +7801,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132989707</v>
+        <v>132989720</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>633839</v>
+        <v>633550</v>
       </c>
       <c r="R65" t="n">
-        <v>7009257</v>
+        <v>7009733</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7908,32 +7908,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132989720</v>
+        <v>132989707</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>633550</v>
+        <v>633839</v>
       </c>
       <c r="R66" t="n">
-        <v>7009733</v>
+        <v>7009257</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8122,10 +8122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133067806</v>
+        <v>133067818</v>
       </c>
       <c r="B68" t="n">
-        <v>92217</v>
+        <v>89300</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8157,13 +8157,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>633605</v>
+        <v>633537</v>
       </c>
       <c r="R68" t="n">
-        <v>7009728</v>
+        <v>7009784</v>
       </c>
       <c r="S68" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133067792</v>
+        <v>133067754</v>
       </c>
       <c r="B69" t="n">
-        <v>89300</v>
+        <v>92217</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>633688</v>
+        <v>633335</v>
       </c>
       <c r="R69" t="n">
-        <v>7009675</v>
+        <v>7009491</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133067818</v>
+        <v>133067792</v>
       </c>
       <c r="B70" t="n">
         <v>89300</v>
@@ -8351,13 +8351,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>633537</v>
+        <v>633688</v>
       </c>
       <c r="R70" t="n">
-        <v>7009784</v>
+        <v>7009675</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133067754</v>
+        <v>133067806</v>
       </c>
       <c r="B71" t="n">
         <v>92217</v>
@@ -8448,13 +8448,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>633335</v>
+        <v>633605</v>
       </c>
       <c r="R71" t="n">
-        <v>7009491</v>
+        <v>7009728</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8510,48 +8510,51 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133067757</v>
+        <v>133067778</v>
       </c>
       <c r="B72" t="n">
-        <v>92217</v>
+        <v>92614</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>633459</v>
+        <v>633719</v>
       </c>
       <c r="R72" t="n">
-        <v>7009486</v>
+        <v>7009606</v>
       </c>
       <c r="S72" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8589,6 +8592,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8607,51 +8611,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133067778</v>
+        <v>133067770</v>
       </c>
       <c r="B73" t="n">
-        <v>92614</v>
+        <v>91881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>633719</v>
+        <v>633791</v>
       </c>
       <c r="R73" t="n">
-        <v>7009606</v>
+        <v>7009345</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8689,7 +8690,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8708,32 +8708,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133067770</v>
+        <v>133067757</v>
       </c>
       <c r="B74" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>633791</v>
+        <v>633459</v>
       </c>
       <c r="R74" t="n">
-        <v>7009345</v>
+        <v>7009486</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8805,48 +8805,51 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133067816</v>
+        <v>133067776</v>
       </c>
       <c r="B75" t="n">
-        <v>91918</v>
+        <v>92378</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>633551</v>
+        <v>633835</v>
       </c>
       <c r="R75" t="n">
-        <v>7009773</v>
+        <v>7009450</v>
       </c>
       <c r="S75" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8884,6 +8887,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8902,51 +8906,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133067776</v>
+        <v>133067816</v>
       </c>
       <c r="B76" t="n">
-        <v>92378</v>
+        <v>91918</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>633835</v>
+        <v>633551</v>
       </c>
       <c r="R76" t="n">
-        <v>7009450</v>
+        <v>7009773</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8984,7 +8985,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9100,10 +9100,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133067790</v>
+        <v>133067761</v>
       </c>
       <c r="B78" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9111,21 +9111,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9135,13 +9135,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>633692</v>
+        <v>633642</v>
       </c>
       <c r="R78" t="n">
-        <v>7009685</v>
+        <v>7009426</v>
       </c>
       <c r="S78" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9171,6 +9171,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9197,10 +9202,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133067761</v>
+        <v>133067790</v>
       </c>
       <c r="B79" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9208,21 +9213,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9232,13 +9237,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>633642</v>
+        <v>633692</v>
       </c>
       <c r="R79" t="n">
-        <v>7009426</v>
+        <v>7009685</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9268,11 +9273,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9600,10 +9600,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133067803</v>
+        <v>133067762</v>
       </c>
       <c r="B83" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9611,21 +9611,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9635,13 +9635,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>633650</v>
+        <v>633703</v>
       </c>
       <c r="R83" t="n">
-        <v>7009698</v>
+        <v>7009368</v>
       </c>
       <c r="S83" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9697,32 +9697,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133067797</v>
+        <v>133067803</v>
       </c>
       <c r="B84" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9732,13 +9732,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>633707</v>
+        <v>633650</v>
       </c>
       <c r="R84" t="n">
-        <v>7009722</v>
+        <v>7009698</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9768,11 +9768,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9799,32 +9794,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133067762</v>
+        <v>133067797</v>
       </c>
       <c r="B85" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9834,13 +9829,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>633703</v>
+        <v>633707</v>
       </c>
       <c r="R85" t="n">
-        <v>7009368</v>
+        <v>7009722</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9870,6 +9865,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9896,10 +9896,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133067800</v>
+        <v>133067768</v>
       </c>
       <c r="B86" t="n">
-        <v>92217</v>
+        <v>57955</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9907,21 +9907,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9931,13 +9931,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>633706</v>
+        <v>633718</v>
       </c>
       <c r="R86" t="n">
-        <v>7009741</v>
+        <v>7009343</v>
       </c>
       <c r="S86" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9993,32 +9993,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133067768</v>
+        <v>133067766</v>
       </c>
       <c r="B87" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>633718</v>
+        <v>633699</v>
       </c>
       <c r="R87" t="n">
-        <v>7009343</v>
+        <v>7009355</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10064,6 +10064,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10090,32 +10095,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133067766</v>
+        <v>133067800</v>
       </c>
       <c r="B88" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10125,13 +10130,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>633699</v>
+        <v>633706</v>
       </c>
       <c r="R88" t="n">
-        <v>7009355</v>
+        <v>7009741</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10161,11 +10166,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10488,7 +10488,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133067785</v>
+        <v>133067758</v>
       </c>
       <c r="B92" t="n">
         <v>91918</v>
@@ -10523,13 +10523,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>633692</v>
+        <v>633460</v>
       </c>
       <c r="R92" t="n">
-        <v>7009685</v>
+        <v>7009486</v>
       </c>
       <c r="S92" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133067758</v>
+        <v>133067785</v>
       </c>
       <c r="B93" t="n">
         <v>91918</v>
@@ -10620,13 +10620,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>633460</v>
+        <v>633692</v>
       </c>
       <c r="R93" t="n">
-        <v>7009486</v>
+        <v>7009685</v>
       </c>
       <c r="S93" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133067794</v>
+        <v>133067773</v>
       </c>
       <c r="B97" t="n">
         <v>79333</v>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>633693</v>
+        <v>633849</v>
       </c>
       <c r="R97" t="n">
-        <v>7009699</v>
+        <v>7009402</v>
       </c>
       <c r="S97" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133067773</v>
+        <v>133067794</v>
       </c>
       <c r="B98" t="n">
         <v>79333</v>
@@ -11105,13 +11105,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>633849</v>
+        <v>633693</v>
       </c>
       <c r="R98" t="n">
-        <v>7009402</v>
+        <v>7009699</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11269,32 +11269,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133067809</v>
+        <v>133067801</v>
       </c>
       <c r="B100" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11304,13 +11304,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>633601</v>
+        <v>633691</v>
       </c>
       <c r="R100" t="n">
-        <v>7009747</v>
+        <v>7009731</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11340,11 +11340,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>20 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11371,32 +11366,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133067801</v>
+        <v>133067809</v>
       </c>
       <c r="B101" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11406,13 +11401,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>633691</v>
+        <v>633601</v>
       </c>
       <c r="R101" t="n">
-        <v>7009731</v>
+        <v>7009747</v>
       </c>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11442,6 +11437,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>20 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11565,51 +11565,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133077248</v>
+        <v>133067781</v>
       </c>
       <c r="B103" t="n">
-        <v>92614</v>
+        <v>92217</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>633835</v>
+        <v>633707</v>
       </c>
       <c r="R103" t="n">
-        <v>7009450</v>
+        <v>7009635</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11641,18 +11638,12 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På samma starkt nedbrutna granlåga som rynkskinn.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11671,48 +11662,51 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133067781</v>
+        <v>133077248</v>
       </c>
       <c r="B104" t="n">
-        <v>92217</v>
+        <v>92614</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>633707</v>
+        <v>633835</v>
       </c>
       <c r="R104" t="n">
-        <v>7009635</v>
+        <v>7009450</v>
       </c>
       <c r="S104" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11744,12 +11738,18 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På samma starkt nedbrutna granlåga som rynkskinn.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12059,32 +12059,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133067775</v>
+        <v>133067819</v>
       </c>
       <c r="B108" t="n">
-        <v>83181</v>
+        <v>80467</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12094,13 +12094,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>633854</v>
+        <v>633552</v>
       </c>
       <c r="R108" t="n">
-        <v>7009413</v>
+        <v>7009791</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12156,32 +12156,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133067819</v>
+        <v>133067775</v>
       </c>
       <c r="B109" t="n">
-        <v>80467</v>
+        <v>83181</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12191,13 +12191,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>633552</v>
+        <v>633854</v>
       </c>
       <c r="R109" t="n">
-        <v>7009791</v>
+        <v>7009413</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132985571</v>
+        <v>132969284</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,37 +1064,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633844</v>
+        <v>633653</v>
       </c>
       <c r="R5" t="n">
-        <v>7009381</v>
+        <v>7009392</v>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,22 +1148,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132969284</v>
+        <v>132985578</v>
       </c>
       <c r="B6" t="n">
-        <v>83181</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633653</v>
+        <v>633735</v>
       </c>
       <c r="R6" t="n">
-        <v>7009392</v>
+        <v>7009705</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,22 +1255,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132985578</v>
+        <v>132985571</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633735</v>
+        <v>633844</v>
       </c>
       <c r="R7" t="n">
-        <v>7009705</v>
+        <v>7009381</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132966472</v>
+        <v>132985582</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,37 +1607,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633653</v>
+        <v>633593</v>
       </c>
       <c r="R10" t="n">
-        <v>7009392</v>
+        <v>7009766</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1684,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spår på halvstubbe, björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132985582</v>
+        <v>132966472</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,45 +1727,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633593</v>
+        <v>633653</v>
       </c>
       <c r="R11" t="n">
-        <v>7009766</v>
+        <v>7009392</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,12 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre spår på halvstubbe, björk.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,12 +1811,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132985568</v>
+        <v>132969471</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,37 +2056,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633641</v>
+        <v>633840</v>
       </c>
       <c r="R14" t="n">
-        <v>7009436</v>
+        <v>7009473</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,22 +2140,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132969471</v>
+        <v>132985568</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,37 +2163,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633840</v>
+        <v>633641</v>
       </c>
       <c r="R15" t="n">
-        <v>7009473</v>
+        <v>7009436</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,12 +2247,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2589,57 +2589,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132975429</v>
+        <v>132985585</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633629</v>
+        <v>633586</v>
       </c>
       <c r="R19" t="n">
-        <v>7009730</v>
+        <v>7009542</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2668,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,12 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>500+</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,19 +2684,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132985585</v>
+        <v>132985572</v>
       </c>
       <c r="B20" t="n">
         <v>79333</v>
@@ -2745,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633586</v>
+        <v>633848</v>
       </c>
       <c r="R20" t="n">
-        <v>7009542</v>
+        <v>7009460</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2780,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,48 +2803,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132985572</v>
+        <v>132975429</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633848</v>
+        <v>633629</v>
       </c>
       <c r="R21" t="n">
-        <v>7009460</v>
+        <v>7009730</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2892,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>500+</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,12 +2912,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4037,56 +4037,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132985576</v>
+        <v>132972132</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633711</v>
+        <v>633840</v>
       </c>
       <c r="R32" t="n">
-        <v>7009713</v>
+        <v>7009473</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4115,7 +4116,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,12 +4126,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,69 +4141,68 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132972132</v>
+        <v>132985576</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartdalskojan, Svartdalskojan, Ång</t>
+          <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>633840</v>
+        <v>633711</v>
       </c>
       <c r="R33" t="n">
-        <v>7009473</v>
+        <v>7009713</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4236,7 +4231,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4241,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4261,12 +4261,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4380,32 +4380,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132985567</v>
+        <v>132985583</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4415,13 +4415,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633458</v>
+        <v>633562</v>
       </c>
       <c r="R35" t="n">
-        <v>7009474</v>
+        <v>7009789</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132985580</v>
+        <v>132985567</v>
       </c>
       <c r="B37" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4605,45 +4605,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633608</v>
+        <v>633458</v>
       </c>
       <c r="R37" t="n">
-        <v>7009719</v>
+        <v>7009474</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4672,7 +4664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4682,7 +4674,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4709,48 +4701,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132985583</v>
+        <v>132985580</v>
       </c>
       <c r="B38" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633562</v>
+        <v>633608</v>
       </c>
       <c r="R38" t="n">
-        <v>7009789</v>
+        <v>7009719</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132989718</v>
+        <v>132989702</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,42 +5903,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>633738</v>
+        <v>633642</v>
       </c>
       <c r="R48" t="n">
-        <v>7009686</v>
+        <v>7009370</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5970,7 +5962,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5980,12 +5972,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6012,10 +5999,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132989702</v>
+        <v>132989718</v>
       </c>
       <c r="B49" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6023,34 +6010,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>633642</v>
+        <v>633738</v>
       </c>
       <c r="R49" t="n">
-        <v>7009370</v>
+        <v>7009686</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6082,7 +6077,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6092,7 +6087,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6444,60 +6444,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132989719</v>
+        <v>132989704</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>633562</v>
+        <v>633780</v>
       </c>
       <c r="R53" t="n">
-        <v>7009774</v>
+        <v>7009330</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6526,7 +6514,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6524,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6545,7 +6533,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6557,7 +6544,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6804,48 +6791,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132989704</v>
+        <v>132989719</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>633780</v>
+        <v>633562</v>
       </c>
       <c r="R56" t="n">
-        <v>7009330</v>
+        <v>7009774</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6874,7 +6873,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6884,7 +6883,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6893,6 +6892,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6904,39 +6904,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132989690</v>
+        <v>132989694</v>
       </c>
       <c r="B57" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>633278</v>
+        <v>633407</v>
       </c>
       <c r="R57" t="n">
-        <v>7009482</v>
+        <v>7009456</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7018,32 +7018,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132989694</v>
+        <v>132989690</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7053,13 +7053,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>633407</v>
+        <v>633278</v>
       </c>
       <c r="R58" t="n">
-        <v>7009456</v>
+        <v>7009482</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7352,53 +7352,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132989696</v>
+        <v>132989691</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>97995</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>633628</v>
+        <v>633305</v>
       </c>
       <c r="R61" t="n">
-        <v>7009444</v>
+        <v>7009515</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -7430,7 +7422,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7440,12 +7432,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7465,52 +7452,60 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Isabelle Åström, Monika Norberg, Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132989691</v>
+        <v>132989696</v>
       </c>
       <c r="B62" t="n">
-        <v>97995</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>633305</v>
+        <v>633628</v>
       </c>
       <c r="R62" t="n">
-        <v>7009515</v>
+        <v>7009444</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7542,7 +7537,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7552,7 +7547,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Isabelle Åström, Monika Norberg, Maria Danvind</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7801,32 +7801,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132989720</v>
+        <v>132989707</v>
       </c>
       <c r="B65" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>633550</v>
+        <v>633839</v>
       </c>
       <c r="R65" t="n">
-        <v>7009733</v>
+        <v>7009257</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7908,32 +7908,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132989707</v>
+        <v>132989720</v>
       </c>
       <c r="B66" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>633839</v>
+        <v>633550</v>
       </c>
       <c r="R66" t="n">
-        <v>7009257</v>
+        <v>7009733</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8122,7 +8122,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133067818</v>
+        <v>133067792</v>
       </c>
       <c r="B68" t="n">
         <v>89300</v>
@@ -8157,13 +8157,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>633537</v>
+        <v>633688</v>
       </c>
       <c r="R68" t="n">
-        <v>7009784</v>
+        <v>7009675</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133067754</v>
+        <v>133067818</v>
       </c>
       <c r="B69" t="n">
-        <v>92217</v>
+        <v>89300</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>633335</v>
+        <v>633537</v>
       </c>
       <c r="R69" t="n">
-        <v>7009491</v>
+        <v>7009784</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133067792</v>
+        <v>133067754</v>
       </c>
       <c r="B70" t="n">
-        <v>89300</v>
+        <v>92217</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8351,13 +8351,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>633688</v>
+        <v>633335</v>
       </c>
       <c r="R70" t="n">
-        <v>7009675</v>
+        <v>7009491</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8510,51 +8510,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133067778</v>
+        <v>133067757</v>
       </c>
       <c r="B72" t="n">
-        <v>92614</v>
+        <v>92217</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>633719</v>
+        <v>633459</v>
       </c>
       <c r="R72" t="n">
-        <v>7009606</v>
+        <v>7009486</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8592,7 +8589,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8611,48 +8607,51 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133067770</v>
+        <v>133067778</v>
       </c>
       <c r="B73" t="n">
-        <v>91881</v>
+        <v>92614</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>633791</v>
+        <v>633719</v>
       </c>
       <c r="R73" t="n">
-        <v>7009345</v>
+        <v>7009606</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8690,6 +8689,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8708,32 +8708,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133067757</v>
+        <v>133067770</v>
       </c>
       <c r="B74" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>633459</v>
+        <v>633791</v>
       </c>
       <c r="R74" t="n">
-        <v>7009486</v>
+        <v>7009345</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8805,51 +8805,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133067776</v>
+        <v>133067816</v>
       </c>
       <c r="B75" t="n">
-        <v>92378</v>
+        <v>91918</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>633835</v>
+        <v>633551</v>
       </c>
       <c r="R75" t="n">
-        <v>7009450</v>
+        <v>7009773</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8887,7 +8884,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8906,48 +8902,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133067816</v>
+        <v>133067776</v>
       </c>
       <c r="B76" t="n">
-        <v>91918</v>
+        <v>92378</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>633551</v>
+        <v>633835</v>
       </c>
       <c r="R76" t="n">
-        <v>7009773</v>
+        <v>7009450</v>
       </c>
       <c r="S76" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8985,6 +8984,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9100,10 +9100,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133067761</v>
+        <v>133067790</v>
       </c>
       <c r="B78" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9111,21 +9111,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9135,13 +9135,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>633642</v>
+        <v>633692</v>
       </c>
       <c r="R78" t="n">
-        <v>7009426</v>
+        <v>7009685</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9171,11 +9171,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9202,10 +9197,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133067790</v>
+        <v>133067761</v>
       </c>
       <c r="B79" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9213,21 +9208,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9237,13 +9232,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>633692</v>
+        <v>633642</v>
       </c>
       <c r="R79" t="n">
-        <v>7009685</v>
+        <v>7009426</v>
       </c>
       <c r="S79" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9273,6 +9268,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9299,32 +9299,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133067814</v>
+        <v>133067772</v>
       </c>
       <c r="B80" t="n">
-        <v>99130</v>
+        <v>89300</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>633565</v>
+        <v>633845</v>
       </c>
       <c r="R80" t="n">
-        <v>7009735</v>
+        <v>7009400</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9370,11 +9370,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ca 20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9401,32 +9396,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133067772</v>
+        <v>133067814</v>
       </c>
       <c r="B81" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9436,13 +9431,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>633845</v>
+        <v>633565</v>
       </c>
       <c r="R81" t="n">
-        <v>7009400</v>
+        <v>7009735</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9472,6 +9467,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ca 20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9600,32 +9600,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133067762</v>
+        <v>133067797</v>
       </c>
       <c r="B83" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9635,13 +9635,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>633703</v>
+        <v>633707</v>
       </c>
       <c r="R83" t="n">
-        <v>7009368</v>
+        <v>7009722</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9671,6 +9671,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9794,32 +9799,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133067797</v>
+        <v>133067762</v>
       </c>
       <c r="B85" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9829,13 +9834,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>633707</v>
+        <v>633703</v>
       </c>
       <c r="R85" t="n">
-        <v>7009722</v>
+        <v>7009368</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9865,11 +9870,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9896,10 +9896,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133067768</v>
+        <v>133067800</v>
       </c>
       <c r="B86" t="n">
-        <v>57955</v>
+        <v>92217</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9907,21 +9907,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9931,13 +9931,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>633718</v>
+        <v>633706</v>
       </c>
       <c r="R86" t="n">
-        <v>7009343</v>
+        <v>7009741</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9993,32 +9993,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133067766</v>
+        <v>133067768</v>
       </c>
       <c r="B87" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>633699</v>
+        <v>633718</v>
       </c>
       <c r="R87" t="n">
-        <v>7009355</v>
+        <v>7009343</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10064,11 +10064,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10095,32 +10090,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133067800</v>
+        <v>133067766</v>
       </c>
       <c r="B88" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10130,13 +10125,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>633706</v>
+        <v>633699</v>
       </c>
       <c r="R88" t="n">
-        <v>7009741</v>
+        <v>7009355</v>
       </c>
       <c r="S88" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10166,6 +10161,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10488,7 +10488,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133067758</v>
+        <v>133067785</v>
       </c>
       <c r="B92" t="n">
         <v>91918</v>
@@ -10523,13 +10523,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>633460</v>
+        <v>633692</v>
       </c>
       <c r="R92" t="n">
-        <v>7009486</v>
+        <v>7009685</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133067785</v>
+        <v>133067758</v>
       </c>
       <c r="B93" t="n">
         <v>91918</v>
@@ -10620,13 +10620,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>633692</v>
+        <v>633460</v>
       </c>
       <c r="R93" t="n">
-        <v>7009685</v>
+        <v>7009486</v>
       </c>
       <c r="S93" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10682,10 +10682,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133067771</v>
+        <v>133067823</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10693,21 +10693,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10717,13 +10717,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>633826</v>
+        <v>633543</v>
       </c>
       <c r="R94" t="n">
-        <v>7009369</v>
+        <v>7009795</v>
       </c>
       <c r="S94" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10779,10 +10779,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133067826</v>
+        <v>133067773</v>
       </c>
       <c r="B95" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10790,21 +10790,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10814,13 +10814,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>633546</v>
+        <v>633849</v>
       </c>
       <c r="R95" t="n">
-        <v>7009736</v>
+        <v>7009402</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10876,10 +10876,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133067823</v>
+        <v>133067771</v>
       </c>
       <c r="B96" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,21 +10887,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10911,13 +10911,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>633543</v>
+        <v>633826</v>
       </c>
       <c r="R96" t="n">
-        <v>7009795</v>
+        <v>7009369</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10973,10 +10973,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133067773</v>
+        <v>133067826</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10984,21 +10984,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>633849</v>
+        <v>633546</v>
       </c>
       <c r="R97" t="n">
-        <v>7009402</v>
+        <v>7009736</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11565,48 +11565,51 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133067781</v>
+        <v>133077248</v>
       </c>
       <c r="B103" t="n">
-        <v>92217</v>
+        <v>92614</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>633707</v>
+        <v>633835</v>
       </c>
       <c r="R103" t="n">
-        <v>7009635</v>
+        <v>7009450</v>
       </c>
       <c r="S103" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11638,12 +11641,18 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På samma starkt nedbrutna granlåga som rynkskinn.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11662,51 +11671,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133077248</v>
+        <v>133067781</v>
       </c>
       <c r="B104" t="n">
-        <v>92614</v>
+        <v>92217</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>633835</v>
+        <v>633707</v>
       </c>
       <c r="R104" t="n">
-        <v>7009450</v>
+        <v>7009635</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11738,18 +11744,12 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På samma starkt nedbrutna granlåga som rynkskinn.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11768,32 +11768,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133067783</v>
+        <v>133067763</v>
       </c>
       <c r="B105" t="n">
-        <v>92217</v>
+        <v>80467</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11803,13 +11803,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>633708</v>
+        <v>633697</v>
       </c>
       <c r="R105" t="n">
-        <v>7009648</v>
+        <v>7009345</v>
       </c>
       <c r="S105" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11865,32 +11865,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133067763</v>
+        <v>133067783</v>
       </c>
       <c r="B106" t="n">
-        <v>80467</v>
+        <v>92217</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11900,13 +11900,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>633697</v>
+        <v>633708</v>
       </c>
       <c r="R106" t="n">
-        <v>7009345</v>
+        <v>7009648</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12251,6 +12251,117 @@
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132989714</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Svartdalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>633694</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7009707</v>
+      </c>
+      <c r="S110" t="n">
+        <v>3</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Markus Borja, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -12256,7 +12256,7 @@
         <v>132989714</v>
       </c>
       <c r="B110" t="n">
-        <v>92304</v>
+        <v>92311</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10712,7 +10712,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132972132</v>
+        <v>132964083</v>
       </c>
       <c r="B96" t="n">
         <v>99195</v>
@@ -10740,26 +10740,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>633840</v>
+        <v>633635</v>
       </c>
       <c r="R96" t="n">
-        <v>7009473</v>
+        <v>7009433</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10791,7 +10782,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10801,7 +10792,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10828,7 +10819,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132972224</v>
+        <v>132972132</v>
       </c>
       <c r="B97" t="n">
         <v>99195</v>
@@ -10872,10 +10863,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>633696</v>
+        <v>633840</v>
       </c>
       <c r="R97" t="n">
-        <v>7009597</v>
+        <v>7009473</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10907,7 +10898,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10917,7 +10908,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10944,7 +10935,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132972743</v>
+        <v>132972224</v>
       </c>
       <c r="B98" t="n">
         <v>99195</v>
@@ -10974,7 +10965,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10988,10 +10979,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>633688</v>
+        <v>633696</v>
       </c>
       <c r="R98" t="n">
-        <v>7009606</v>
+        <v>7009597</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11023,7 +11014,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11033,7 +11024,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11060,7 +11051,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132973056</v>
+        <v>132972743</v>
       </c>
       <c r="B99" t="n">
         <v>99195</v>
@@ -11090,7 +11081,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11104,10 +11095,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>633682</v>
+        <v>633688</v>
       </c>
       <c r="R99" t="n">
-        <v>7009654</v>
+        <v>7009606</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11139,7 +11130,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11149,7 +11140,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11176,7 +11167,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132975429</v>
+        <v>132973056</v>
       </c>
       <c r="B100" t="n">
         <v>99195</v>
@@ -11206,7 +11197,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11220,13 +11211,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>633629</v>
+        <v>633682</v>
       </c>
       <c r="R100" t="n">
-        <v>7009730</v>
+        <v>7009654</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11255,7 +11246,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11265,12 +11256,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>500+</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11290,14 +11276,14 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132977000</v>
+        <v>132975429</v>
       </c>
       <c r="B101" t="n">
         <v>99195</v>
@@ -11327,7 +11313,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -11341,10 +11327,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>633575</v>
+        <v>633629</v>
       </c>
       <c r="R101" t="n">
-        <v>7009754</v>
+        <v>7009730</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11376,7 +11362,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11386,7 +11372,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>500+</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11413,7 +11404,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132989698</v>
+        <v>132977000</v>
       </c>
       <c r="B102" t="n">
         <v>99195</v>
@@ -11443,7 +11434,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11451,22 +11442,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>633608</v>
+        <v>633575</v>
       </c>
       <c r="R102" t="n">
-        <v>7009455</v>
+        <v>7009754</v>
       </c>
       <c r="S102" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11495,7 +11483,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11505,7 +11493,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11514,26 +11502,25 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Isabelle Åström, Monika Norberg, Maria Danvind</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132989700</v>
+        <v>132989698</v>
       </c>
       <c r="B103" t="n">
         <v>99195</v>
@@ -11563,7 +11550,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11580,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>633634</v>
+        <v>633608</v>
       </c>
       <c r="R103" t="n">
-        <v>7009438</v>
+        <v>7009455</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -11615,7 +11602,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11625,7 +11612,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11646,14 +11633,14 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg</t>
+          <t>Markus Borja, Ann-Christine Borja, Isabelle Åström, Monika Norberg, Maria Danvind</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132989719</v>
+        <v>132989700</v>
       </c>
       <c r="B104" t="n">
         <v>99195</v>
@@ -11683,7 +11670,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11700,10 +11687,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>633562</v>
+        <v>633634</v>
       </c>
       <c r="R104" t="n">
-        <v>7009774</v>
+        <v>7009438</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
@@ -11735,7 +11722,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11745,7 +11732,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11766,14 +11753,14 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132989721</v>
+        <v>132989719</v>
       </c>
       <c r="B105" t="n">
         <v>99195</v>
@@ -11803,7 +11790,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11820,10 +11807,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>633571</v>
+        <v>633562</v>
       </c>
       <c r="R105" t="n">
-        <v>7009703</v>
+        <v>7009774</v>
       </c>
       <c r="S105" t="n">
         <v>3</v>
@@ -11855,7 +11842,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11865,7 +11852,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11886,14 +11873,14 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133067766</v>
+        <v>132989721</v>
       </c>
       <c r="B106" t="n">
         <v>99195</v>
@@ -11921,20 +11908,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>633699</v>
+        <v>633571</v>
       </c>
       <c r="R106" t="n">
-        <v>7009355</v>
+        <v>7009703</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11961,14 +11960,19 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>20 plantor</t>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11977,25 +11981,26 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133067797</v>
+        <v>133067766</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -12030,13 +12035,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>633707</v>
+        <v>633699</v>
       </c>
       <c r="R107" t="n">
-        <v>7009722</v>
+        <v>7009355</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12070,7 +12075,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ca 100.</t>
+          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12097,7 +12102,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133067809</v>
+        <v>133067797</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -12132,13 +12137,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>633601</v>
+        <v>633707</v>
       </c>
       <c r="R108" t="n">
-        <v>7009747</v>
+        <v>7009722</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12172,7 +12177,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>20 st</t>
+          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12199,7 +12204,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133067811</v>
+        <v>133067809</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -12234,10 +12239,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>633597</v>
+        <v>633601</v>
       </c>
       <c r="R109" t="n">
-        <v>7009754</v>
+        <v>7009747</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12274,7 +12279,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ca 175</t>
+          <t>20 st</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12301,7 +12306,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133067814</v>
+        <v>133067811</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -12336,10 +12341,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>633565</v>
+        <v>633597</v>
       </c>
       <c r="R110" t="n">
-        <v>7009735</v>
+        <v>7009754</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12376,7 +12381,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ca 20</t>
+          <t>Ca 175</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12403,7 +12408,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133067829</v>
+        <v>133067814</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -12438,13 +12443,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>633610</v>
+        <v>633565</v>
       </c>
       <c r="R111" t="n">
-        <v>7009652</v>
+        <v>7009735</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12478,7 +12483,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Ca 20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12505,32 +12510,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132985565</v>
+        <v>133067829</v>
       </c>
       <c r="B112" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12540,13 +12545,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>633313</v>
+        <v>633610</v>
       </c>
       <c r="R112" t="n">
-        <v>7009500</v>
+        <v>7009652</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12573,19 +12578,14 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:38</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12600,19 +12600,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132985583</v>
+        <v>132985565</v>
       </c>
       <c r="B113" t="n">
         <v>98060</v>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>633562</v>
+        <v>633313</v>
       </c>
       <c r="R113" t="n">
-        <v>7009789</v>
+        <v>7009500</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12719,7 +12719,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132989689</v>
+        <v>132985583</v>
       </c>
       <c r="B114" t="n">
         <v>98060</v>
@@ -12754,13 +12754,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>633212</v>
+        <v>633562</v>
       </c>
       <c r="R114" t="n">
-        <v>7009460</v>
+        <v>7009789</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12814,19 +12814,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132989690</v>
+        <v>132989689</v>
       </c>
       <c r="B115" t="n">
         <v>98060</v>
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>633278</v>
+        <v>633212</v>
       </c>
       <c r="R115" t="n">
-        <v>7009482</v>
+        <v>7009460</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12933,7 +12933,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132989691</v>
+        <v>132989690</v>
       </c>
       <c r="B116" t="n">
         <v>98060</v>
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>633305</v>
+        <v>633278</v>
       </c>
       <c r="R116" t="n">
-        <v>7009515</v>
+        <v>7009482</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13037,6 +13037,113 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>132989691</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Svartdalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>633305</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7009515</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AZ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/165289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067772</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985579</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989692</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989693</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989710</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067754</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067781</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2004,6 +2069,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067783</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067790</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067800</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2295,6 +2375,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067806</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,6 +2481,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067778</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067825</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133077248</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132964132</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132969471</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2920,6 +3030,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972951</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985564</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,6 +3254,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989694</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3241,6 +3366,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989701</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3348,6 +3478,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989702</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3455,6 +3590,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989704</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989707</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3669,6 +3814,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989708</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3766,6 +3916,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067758</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3863,6 +4018,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067762</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3960,6 +4120,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067769</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4057,6 +4222,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067771</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4154,6 +4324,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067785</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4251,6 +4426,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067801</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4348,6 +4528,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067816</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4445,6 +4630,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067826</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4557,6 +4747,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Skogsbruksplan Björkå bruk</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/384817</t>
         </is>
       </c>
     </row>
@@ -4670,6 +4865,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989709</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4771,6 +4971,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067776</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4878,6 +5083,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132969284</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4975,6 +5185,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067775</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5086,6 +5301,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989714</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5193,6 +5413,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132971223</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5300,6 +5525,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989720</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5397,6 +5627,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067756</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5494,6 +5729,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067770</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5601,6 +5841,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132966472</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5708,6 +5953,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985566</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5815,6 +6065,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985567</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5922,6 +6177,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985568</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6029,6 +6289,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985571</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6136,6 +6401,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985572</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6243,6 +6513,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985574</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6350,6 +6625,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985584</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6457,6 +6737,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985585</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6583,6 +6868,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989706</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6709,6 +6999,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989711</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6835,6 +7130,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989722</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6932,6 +7232,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067773</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7029,6 +7334,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067794</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7126,6 +7436,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067803</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7223,6 +7538,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067823</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7320,6 +7640,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067831</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7427,6 +7752,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132977419</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7524,6 +7854,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067763</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7621,6 +7956,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067819</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7718,6 +8058,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067821</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7825,6 +8170,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985569</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7940,6 +8290,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985573</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8047,6 +8402,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985578</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8162,6 +8522,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985580</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8277,6 +8642,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985581</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8397,6 +8767,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985582</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8512,6 +8887,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989703</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8614,6 +8994,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067755</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8716,6 +9101,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067767</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8828,6 +9218,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132979500</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8948,6 +9343,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985576</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9068,6 +9468,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985577</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9188,6 +9593,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989695</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9308,6 +9718,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989696</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9428,6 +9843,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989699</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9548,6 +9968,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989712</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9668,6 +10093,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989715</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9788,6 +10218,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989718</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9890,6 +10325,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067760</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9992,6 +10432,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067761</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10116,6 +10561,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989723</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10240,6 +10690,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134226245</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10364,6 +10819,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134226224</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10479,6 +10939,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112622346</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10594,6 +11059,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985570</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10709,6 +11179,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985575</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10816,6 +11291,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132964083</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10932,6 +11412,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972132</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11048,6 +11533,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972224</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11164,6 +11654,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972743</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11280,6 +11775,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132973056</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11401,6 +11901,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132975429</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11517,6 +12022,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132977000</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11637,6 +12147,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989698</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11757,6 +12272,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989700</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11877,6 +12397,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989719</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11997,6 +12522,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989721</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12099,6 +12629,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067766</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12201,6 +12736,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067797</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12303,6 +12843,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067809</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12405,6 +12950,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067811</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12507,6 +13057,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067814</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12609,6 +13164,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133067829</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12716,6 +13276,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985565</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12823,6 +13388,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132985583</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12930,6 +13500,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989689</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13037,6 +13612,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989690</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13144,8 +13724,131 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989691</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -11190,7 +11190,7 @@
         <v>132964083</v>
       </c>
       <c r="B96" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -11190,7 +11190,7 @@
         <v>132964083</v>
       </c>
       <c r="B96" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ116"/>
+  <dimension ref="A1:AZ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11187,10 +11187,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132972132</v>
+        <v>132964083</v>
       </c>
       <c r="B96" t="n">
-        <v>99195</v>
+        <v>99274</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11215,26 +11215,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>633840</v>
+        <v>633635</v>
       </c>
       <c r="R96" t="n">
-        <v>7009473</v>
+        <v>7009433</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -11266,7 +11257,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11276,7 +11267,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11302,13 +11293,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132972132</t>
+          <t>https://artportalen.se/Sighting/132964083</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132972224</v>
+        <v>132972132</v>
       </c>
       <c r="B97" t="n">
         <v>99195</v>
@@ -11352,10 +11343,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>633696</v>
+        <v>633840</v>
       </c>
       <c r="R97" t="n">
-        <v>7009597</v>
+        <v>7009473</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11387,7 +11378,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11397,7 +11388,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11423,13 +11414,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132972224</t>
+          <t>https://artportalen.se/Sighting/132972132</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132972743</v>
+        <v>132972224</v>
       </c>
       <c r="B98" t="n">
         <v>99195</v>
@@ -11459,7 +11450,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11473,10 +11464,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>633688</v>
+        <v>633696</v>
       </c>
       <c r="R98" t="n">
-        <v>7009606</v>
+        <v>7009597</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11508,7 +11499,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11518,7 +11509,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11544,13 +11535,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132972743</t>
+          <t>https://artportalen.se/Sighting/132972224</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132973056</v>
+        <v>132972743</v>
       </c>
       <c r="B99" t="n">
         <v>99195</v>
@@ -11580,7 +11571,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11594,10 +11585,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>633682</v>
+        <v>633688</v>
       </c>
       <c r="R99" t="n">
-        <v>7009654</v>
+        <v>7009606</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11629,7 +11620,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11639,7 +11630,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11665,13 +11656,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132973056</t>
+          <t>https://artportalen.se/Sighting/132972743</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132975429</v>
+        <v>132973056</v>
       </c>
       <c r="B100" t="n">
         <v>99195</v>
@@ -11701,7 +11692,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11715,13 +11706,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>633629</v>
+        <v>633682</v>
       </c>
       <c r="R100" t="n">
-        <v>7009730</v>
+        <v>7009654</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11750,7 +11741,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11760,12 +11751,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:21</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>500+</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11785,19 +11771,19 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Monika Norberg, Monika Norberg</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132975429</t>
+          <t>https://artportalen.se/Sighting/132973056</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132977000</v>
+        <v>132975429</v>
       </c>
       <c r="B101" t="n">
         <v>99195</v>
@@ -11827,7 +11813,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -11841,10 +11827,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>633575</v>
+        <v>633629</v>
       </c>
       <c r="R101" t="n">
-        <v>7009754</v>
+        <v>7009730</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11876,7 +11862,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11886,7 +11872,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>500+</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11912,13 +11903,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132977000</t>
+          <t>https://artportalen.se/Sighting/132975429</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132989698</v>
+        <v>132977000</v>
       </c>
       <c r="B102" t="n">
         <v>99195</v>
@@ -11948,7 +11939,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11956,22 +11947,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Svartdalen, Ång</t>
+          <t>Svartdalskojan, Svartdalskojan, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>633608</v>
+        <v>633575</v>
       </c>
       <c r="R102" t="n">
-        <v>7009455</v>
+        <v>7009754</v>
       </c>
       <c r="S102" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12000,7 +11988,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12010,7 +11998,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12019,31 +12007,30 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Isabelle Åström, Monika Norberg, Maria Danvind</t>
+          <t>Monika Norberg, Monika Norberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132989698</t>
+          <t>https://artportalen.se/Sighting/132977000</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132989700</v>
+        <v>132989698</v>
       </c>
       <c r="B103" t="n">
         <v>99195</v>
@@ -12073,7 +12060,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12090,10 +12077,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>633634</v>
+        <v>633608</v>
       </c>
       <c r="R103" t="n">
-        <v>7009438</v>
+        <v>7009455</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -12125,7 +12112,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12135,7 +12122,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12156,19 +12143,19 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg</t>
+          <t>Markus Borja, Ann-Christine Borja, Isabelle Åström, Monika Norberg, Maria Danvind</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132989700</t>
+          <t>https://artportalen.se/Sighting/132989698</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132989719</v>
+        <v>132989700</v>
       </c>
       <c r="B104" t="n">
         <v>99195</v>
@@ -12198,7 +12185,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12215,10 +12202,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>633562</v>
+        <v>633634</v>
       </c>
       <c r="R104" t="n">
-        <v>7009774</v>
+        <v>7009438</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
@@ -12250,7 +12237,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12260,7 +12247,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12281,19 +12268,19 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132989719</t>
+          <t>https://artportalen.se/Sighting/132989700</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132989721</v>
+        <v>132989719</v>
       </c>
       <c r="B105" t="n">
         <v>99195</v>
@@ -12323,7 +12310,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12340,10 +12327,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>633571</v>
+        <v>633562</v>
       </c>
       <c r="R105" t="n">
-        <v>7009703</v>
+        <v>7009774</v>
       </c>
       <c r="S105" t="n">
         <v>3</v>
@@ -12375,7 +12362,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12385,7 +12372,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12406,19 +12393,19 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Maria Danvind, Monika Norberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132989721</t>
+          <t>https://artportalen.se/Sighting/132989719</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133067766</v>
+        <v>132989721</v>
       </c>
       <c r="B106" t="n">
         <v>99195</v>
@@ -12446,20 +12433,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svartdalen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>633699</v>
+        <v>633571</v>
       </c>
       <c r="R106" t="n">
-        <v>7009355</v>
+        <v>7009703</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12486,14 +12485,19 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>20 plantor</t>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12502,30 +12506,31 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067766</t>
+          <t>https://artportalen.se/Sighting/132989721</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133067797</v>
+        <v>133067766</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -12560,13 +12565,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>633707</v>
+        <v>633699</v>
       </c>
       <c r="R107" t="n">
-        <v>7009722</v>
+        <v>7009355</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12600,7 +12605,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ca 100.</t>
+          <t>20 plantor</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12626,13 +12631,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067797</t>
+          <t>https://artportalen.se/Sighting/133067766</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133067809</v>
+        <v>133067797</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -12667,13 +12672,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>633601</v>
+        <v>633707</v>
       </c>
       <c r="R108" t="n">
-        <v>7009747</v>
+        <v>7009722</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12707,7 +12712,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>20 st</t>
+          <t>Ca 100.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12733,13 +12738,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067809</t>
+          <t>https://artportalen.se/Sighting/133067797</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133067811</v>
+        <v>133067809</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -12774,10 +12779,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>633597</v>
+        <v>633601</v>
       </c>
       <c r="R109" t="n">
-        <v>7009754</v>
+        <v>7009747</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12814,7 +12819,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ca 175</t>
+          <t>20 st</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12840,13 +12845,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067811</t>
+          <t>https://artportalen.se/Sighting/133067809</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133067814</v>
+        <v>133067811</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -12881,10 +12886,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>633565</v>
+        <v>633597</v>
       </c>
       <c r="R110" t="n">
-        <v>7009735</v>
+        <v>7009754</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12921,7 +12926,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ca 20</t>
+          <t>Ca 175</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12947,13 +12952,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067814</t>
+          <t>https://artportalen.se/Sighting/133067811</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133067829</v>
+        <v>133067814</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -12988,13 +12993,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>633610</v>
+        <v>633565</v>
       </c>
       <c r="R111" t="n">
-        <v>7009652</v>
+        <v>7009735</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13028,7 +13033,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Ca 20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13054,38 +13059,38 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133067829</t>
+          <t>https://artportalen.se/Sighting/133067814</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132985565</v>
+        <v>133067829</v>
       </c>
       <c r="B112" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13095,13 +13100,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>633313</v>
+        <v>633610</v>
       </c>
       <c r="R112" t="n">
-        <v>7009500</v>
+        <v>7009652</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13128,19 +13133,14 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:38</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13155,24 +13155,24 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132985565</t>
+          <t>https://artportalen.se/Sighting/133067829</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132985583</v>
+        <v>132985565</v>
       </c>
       <c r="B113" t="n">
         <v>98060</v>
@@ -13207,13 +13207,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>633562</v>
+        <v>633313</v>
       </c>
       <c r="R113" t="n">
-        <v>7009789</v>
+        <v>7009500</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13278,13 +13278,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132985583</t>
+          <t>https://artportalen.se/Sighting/132985565</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132989689</v>
+        <v>132985583</v>
       </c>
       <c r="B114" t="n">
         <v>98060</v>
@@ -13319,13 +13319,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>633212</v>
+        <v>633562</v>
       </c>
       <c r="R114" t="n">
-        <v>7009460</v>
+        <v>7009789</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13379,24 +13379,24 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132989689</t>
+          <t>https://artportalen.se/Sighting/132985583</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132989690</v>
+        <v>132989689</v>
       </c>
       <c r="B115" t="n">
         <v>98060</v>
@@ -13431,10 +13431,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>633278</v>
+        <v>633212</v>
       </c>
       <c r="R115" t="n">
-        <v>7009482</v>
+        <v>7009460</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13502,13 +13502,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132989690</t>
+          <t>https://artportalen.se/Sighting/132989689</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132989691</v>
+        <v>132989690</v>
       </c>
       <c r="B116" t="n">
         <v>98060</v>
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>633305</v>
+        <v>633278</v>
       </c>
       <c r="R116" t="n">
-        <v>7009515</v>
+        <v>7009482</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13613,6 +13613,118 @@
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132989690</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>132989691</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Svartdalen, Ång</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>633305</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7009515</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132989691</t>
         </is>
@@ -13735,6 +13847,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17379-2026 artfynd.xlsx
+++ b/artfynd/A 17379-2026 artfynd.xlsx
@@ -11190,7 +11190,7 @@
         <v>132964083</v>
       </c>
       <c r="B96" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
